--- a/outputs/data_quality_results_v3.xlsx
+++ b/outputs/data_quality_results_v3.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-26T12:38:31.797528+00:00</t>
+          <t>2026-07-27T06:01:30.763969+00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
